--- a/astro-site/public/dl/kit-tareas-pizzeria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/05-tareas-semanales-mensuales.xlsx
@@ -791,6 +791,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="23" t="inlineStr">
         <is>
@@ -798,6 +799,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="32" customHeight="1">
       <c r="B24" s="24" t="inlineStr">
         <is>
@@ -812,6 +814,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="23" t="inlineStr">
         <is>
@@ -819,6 +822,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29" ht="16" customHeight="1">
       <c r="B29" s="24" t="inlineStr">
         <is>
@@ -854,6 +858,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="23" t="inlineStr">
         <is>
@@ -861,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37" ht="35" customHeight="1">
       <c r="B37" s="23" t="inlineStr">
         <is>
@@ -875,6 +881,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="23" t="inlineStr">
         <is>
@@ -980,10 +987,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="D6" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="E6" s="10">
         <f>IF(B6="","",IF(B6&lt;D6,"⚠️ PEDIR","OK"))</f>
@@ -1003,10 +1008,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="D7" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="E7" s="14">
         <f>IF(B7="","",IF(B7&lt;D7,"⚠️ PEDIR","OK"))</f>
@@ -1026,10 +1029,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D8" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="E8" s="10">
         <f>IF(B8="","",IF(B8&lt;D8,"⚠️ PEDIR","OK"))</f>
@@ -1049,10 +1050,8 @@
           <t>g</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D9" s="13" t="n">
+        <v>100</v>
       </c>
       <c r="E9" s="14">
         <f>IF(B9="","",IF(B9&lt;D9,"⚠️ PEDIR","OK"))</f>
@@ -1072,10 +1071,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D10" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E10" s="10">
         <f>IF(B10="","",IF(B10&lt;D10,"⚠️ PEDIR","OK"))</f>
@@ -1102,10 +1099,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D12" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E12" s="10">
         <f>IF(B12="","",IF(B12&lt;D12,"⚠️ PEDIR","OK"))</f>
@@ -1125,10 +1120,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="D13" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="E13" s="14">
         <f>IF(B13="","",IF(B13&lt;D13,"⚠️ PEDIR","OK"))</f>
@@ -1148,10 +1141,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E14" s="10">
         <f>IF(B14="","",IF(B14&lt;D14,"⚠️ PEDIR","OK"))</f>
@@ -1171,10 +1162,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D15" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E15" s="14">
         <f>IF(B15="","",IF(B15&lt;D15,"⚠️ PEDIR","OK"))</f>
@@ -1194,10 +1183,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D16" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="E16" s="10">
         <f>IF(B16="","",IF(B16&lt;D16,"⚠️ PEDIR","OK"))</f>
@@ -1224,10 +1211,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="D18" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="E18" s="10">
         <f>IF(B18="","",IF(B18&lt;D18,"⚠️ PEDIR","OK"))</f>
@@ -1247,10 +1232,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="D19" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="E19" s="14">
         <f>IF(B19="","",IF(B19&lt;D19,"⚠️ PEDIR","OK"))</f>
@@ -1270,10 +1253,8 @@
           <t>g</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="D20" s="9" t="n">
+        <v>300</v>
       </c>
       <c r="E20" s="10">
         <f>IF(B20="","",IF(B20&lt;D20,"⚠️ PEDIR","OK"))</f>
@@ -1293,10 +1274,8 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D21" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="E21" s="14">
         <f>IF(B21="","",IF(B21&lt;D21,"⚠️ PEDIR","OK"))</f>
@@ -1316,10 +1295,8 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D22" s="9" t="n">
+        <v>100</v>
       </c>
       <c r="E22" s="10">
         <f>IF(B22="","",IF(B22&lt;D22,"⚠️ PEDIR","OK"))</f>
@@ -1346,10 +1323,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D24" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E24" s="10">
         <f>IF(B24="","",IF(B24&lt;D24,"⚠️ PEDIR","OK"))</f>
@@ -1369,10 +1344,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D25" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="E25" s="14">
         <f>IF(B25="","",IF(B25&lt;D25,"⚠️ PEDIR","OK"))</f>
@@ -1392,10 +1365,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D26" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E26" s="10">
         <f>IF(B26="","",IF(B26&lt;D26,"⚠️ PEDIR","OK"))</f>
@@ -1415,10 +1386,8 @@
           <t>g</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="D27" s="13" t="n">
+        <v>200</v>
       </c>
       <c r="E27" s="14">
         <f>IF(B27="","",IF(B27&lt;D27,"⚠️ PEDIR","OK"))</f>
@@ -1438,10 +1407,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D28" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="E28" s="10">
         <f>IF(B28="","",IF(B28&lt;D28,"⚠️ PEDIR","OK"))</f>
@@ -1468,10 +1435,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="D30" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="E30" s="10">
         <f>IF(B30="","",IF(B30&lt;D30,"⚠️ PEDIR","OK"))</f>
@@ -1491,10 +1456,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D31" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E31" s="14">
         <f>IF(B31="","",IF(B31&lt;D31,"⚠️ PEDIR","OK"))</f>
@@ -1514,10 +1477,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D32" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="E32" s="10">
         <f>IF(B32="","",IF(B32&lt;D32,"⚠️ PEDIR","OK"))</f>
@@ -1537,10 +1498,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D33" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E33" s="14">
         <f>IF(B33="","",IF(B33&lt;D33,"⚠️ PEDIR","OK"))</f>
@@ -1560,10 +1519,8 @@
           <t>g</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="D34" s="9" t="n">
+        <v>200</v>
       </c>
       <c r="E34" s="10">
         <f>IF(B34="","",IF(B34&lt;D34,"⚠️ PEDIR","OK"))</f>
@@ -1583,10 +1540,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="D35" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="E35" s="14">
         <f>IF(B35="","",IF(B35&lt;D35,"⚠️ PEDIR","OK"))</f>
@@ -1606,10 +1561,8 @@
           <t>manojos</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D36" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="E36" s="10">
         <f>IF(B36="","",IF(B36&lt;D36,"⚠️ PEDIR","OK"))</f>
@@ -1636,10 +1589,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D38" s="9" t="n">
+        <v>40</v>
       </c>
       <c r="E38" s="10">
         <f>IF(B38="","",IF(B38&lt;D38,"⚠️ PEDIR","OK"))</f>
@@ -1659,10 +1610,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="D39" s="13" t="n">
+        <v>30</v>
       </c>
       <c r="E39" s="14">
         <f>IF(B39="","",IF(B39&lt;D39,"⚠️ PEDIR","OK"))</f>
@@ -1682,10 +1631,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="D40" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="E40" s="10">
         <f>IF(B40="","",IF(B40&lt;D40,"⚠️ PEDIR","OK"))</f>
@@ -1705,10 +1652,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D41" s="13" t="n">
+        <v>100</v>
       </c>
       <c r="E41" s="14">
         <f>IF(B41="","",IF(B41&lt;D41,"⚠️ PEDIR","OK"))</f>
@@ -1728,10 +1673,8 @@
           <t>uds</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="D42" s="9" t="n">
+        <v>30</v>
       </c>
       <c r="E42" s="10">
         <f>IF(B42="","",IF(B42&lt;D42,"⚠️ PEDIR","OK"))</f>
@@ -1739,6 +1682,7 @@
       </c>
       <c r="F42" s="8" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
@@ -1746,6 +1690,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
@@ -1756,15 +1701,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -2294,7 +2239,7 @@
       </c>
       <c r="D27" s="19">
         <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
@@ -2303,7 +2248,7 @@
       </c>
       <c r="F27">
         <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
-        <v>13.0</v>
+        <v/>
       </c>
     </row>
     <row r="28"/>
@@ -2327,12 +2272,12 @@
   <mergeCells count="8">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G25">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -2778,7 +2723,7 @@
       </c>
       <c r="D23" s="19">
         <f>COUNTIFS(B5:B21,"?*",F5:F21,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
@@ -2787,7 +2732,7 @@
       </c>
       <c r="F23">
         <f>COUNTIF(B5:B21,"?*")-COUNTIF(F5:F21,"N/A")</f>
-        <v>10.0</v>
+        <v/>
       </c>
     </row>
     <row r="24"/>
@@ -2844,6 +2789,9 @@
           <t>El gluten pierde fuerza y la levadura, actividad: descongela 24 h en cámara, nunca a temperatura ambiente</t>
         </is>
       </c>
+      <c r="E29" s="26" t="n"/>
+      <c r="F29" s="26" t="n"/>
+      <c r="G29" s="26" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -2862,6 +2810,9 @@
           <t>La fior di latte fresca en su líquido NO se congela: se rompe y suelta agua sobre la pizza</t>
         </is>
       </c>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+      <c r="G30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -2880,6 +2831,9 @@
           <t>La grasa se enrancia aunque esté congelada: es lo que antes se estropea</t>
         </is>
       </c>
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="26" t="n"/>
+      <c r="G31" s="26" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -2898,6 +2852,9 @@
           <t>Mucha superficie expuesta: la familia más delicada de todas</t>
         </is>
       </c>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+      <c r="G32" s="26" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -2916,6 +2873,9 @@
           <t>Sueltan agua al descongelar: congélalos ya porcionados por servicio</t>
         </is>
       </c>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="n"/>
+      <c r="G33" s="26" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -2934,6 +2894,9 @@
           <t>Etiquetar con fecha de producción Y de congelación: la vida útil de esta tabla se cuenta desde la de congelación</t>
         </is>
       </c>
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="26" t="n"/>
+      <c r="G34" s="26" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -2952,6 +2915,9 @@
           <t>Pierde textura antes que seguridad</t>
         </is>
       </c>
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="26" t="n"/>
+      <c r="G35" s="26" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -2970,6 +2936,9 @@
           <t>Sin escaldar previamente, la mitad</t>
         </is>
       </c>
+      <c r="E36" s="26" t="n"/>
+      <c r="F36" s="26" t="n"/>
+      <c r="G36" s="26" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -2988,6 +2957,9 @@
           <t>El azul y el marisco son los primeros en enranciarse</t>
         </is>
       </c>
+      <c r="E37" s="26" t="n"/>
+      <c r="F37" s="26" t="n"/>
+      <c r="G37" s="26" t="n"/>
     </row>
     <row r="38"/>
     <row r="39">
@@ -3002,22 +2974,22 @@
   <mergeCells count="18">
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D37:G37"/>
     <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D37:G37"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G21">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -3436,7 +3408,7 @@
       </c>
       <c r="D22" s="19">
         <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
@@ -3445,7 +3417,7 @@
       </c>
       <c r="F22">
         <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
-        <v>9.0</v>
+        <v/>
       </c>
     </row>
     <row r="23"/>
@@ -3467,13 +3439,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A26:G26"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -4007,7 +3979,7 @@
       </c>
       <c r="D29" s="19">
         <f>COUNTIFS(B5:B27,"?*",F5:F27,"✓")</f>
-        <v>0.0</v>
+        <v/>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
@@ -4016,7 +3988,7 @@
       </c>
       <c r="F29">
         <f>COUNTIF(B5:B27,"?*")-COUNTIF(F5:F27,"N/A")</f>
-        <v>15.0</v>
+        <v/>
       </c>
     </row>
     <row r="30"/>
@@ -4038,13 +4010,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:G27">

--- a/astro-site/public/dl/kit-tareas-pizzeria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-pizzeria/05-tareas-semanales-mensuales.xlsx
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D27" s="19">
         <f>COUNTIFS(B5:B25,"?*",F5:F25,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="F27">
         <f>COUNTIF(B5:B25,"?*")-COUNTIF(F5:F25,"N/A")</f>
-        <v/>
+        <v>13.0</v>
       </c>
     </row>
     <row r="28"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D23" s="19">
         <f>COUNTIFS(B5:B21,"?*",F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F23">
         <f>COUNTIF(B5:B21,"?*")-COUNTIF(F5:F21,"N/A")</f>
-        <v/>
+        <v>10.0</v>
       </c>
     </row>
     <row r="24"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="D22" s="19">
         <f>COUNTIFS(B5:B20,"?*",F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F22">
         <f>COUNTIF(B5:B20,"?*")-COUNTIF(F5:F20,"N/A")</f>
-        <v/>
+        <v>9.0</v>
       </c>
     </row>
     <row r="23"/>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="D29" s="19">
         <f>COUNTIFS(B5:B27,"?*",F5:F27,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="F29">
         <f>COUNTIF(B5:B27,"?*")-COUNTIF(F5:F27,"N/A")</f>
-        <v/>
+        <v>15.0</v>
       </c>
     </row>
     <row r="30"/>
